--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L393"/>
+  <dimension ref="A1:L394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16954,6 +16954,48 @@
       <c r="L393" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>330.78</v>
+      </c>
+      <c r="C394" t="n">
+        <v>332.06</v>
+      </c>
+      <c r="D394" t="n">
+        <v>338.08</v>
+      </c>
+      <c r="E394" t="n">
+        <v>328.95</v>
+      </c>
+      <c r="F394" t="n">
+        <v>324.63</v>
+      </c>
+      <c r="G394" t="n">
+        <v>315.28</v>
+      </c>
+      <c r="H394" t="n">
+        <v>323.92</v>
+      </c>
+      <c r="I394" t="n">
+        <v>325.64</v>
+      </c>
+      <c r="J394" t="n">
+        <v>325.16</v>
+      </c>
+      <c r="K394" t="n">
+        <v>324.7</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16968,7 +17010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20931,6 +20973,16 @@
       </c>
       <c r="B396" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -21099,28 +21151,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7938027128058843</v>
+        <v>0.7914006359083728</v>
       </c>
       <c r="J2" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K2" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5550238419587563</v>
+        <v>0.5543098920297466</v>
       </c>
       <c r="M2" t="n">
-        <v>4.378170359375111</v>
+        <v>4.377367340225088</v>
       </c>
       <c r="N2" t="n">
-        <v>27.39325978810016</v>
+        <v>27.38236452079129</v>
       </c>
       <c r="O2" t="n">
-        <v>5.233857066074709</v>
+        <v>5.232816117616908</v>
       </c>
       <c r="P2" t="n">
-        <v>314.7800768311263</v>
+        <v>314.8052782644814</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21177,28 +21229,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7717924074787406</v>
+        <v>0.7694162096568385</v>
       </c>
       <c r="J3" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K3" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4899073992043342</v>
+        <v>0.4892675952748334</v>
       </c>
       <c r="M3" t="n">
-        <v>4.69008422986589</v>
+        <v>4.688341921394981</v>
       </c>
       <c r="N3" t="n">
-        <v>33.63020269699906</v>
+        <v>33.60217702795919</v>
       </c>
       <c r="O3" t="n">
-        <v>5.799155343409854</v>
+        <v>5.79673848193613</v>
       </c>
       <c r="P3" t="n">
-        <v>316.5838017573274</v>
+        <v>316.6087316798912</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21255,28 +21307,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4902205275727106</v>
+        <v>0.4884205656745445</v>
       </c>
       <c r="J4" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K4" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3895265993818418</v>
+        <v>0.3886576086967504</v>
       </c>
       <c r="M4" t="n">
-        <v>3.522422709071041</v>
+        <v>3.522411135279517</v>
       </c>
       <c r="N4" t="n">
-        <v>20.42236662233241</v>
+        <v>20.40342205927438</v>
       </c>
       <c r="O4" t="n">
-        <v>4.519111264655077</v>
+        <v>4.517014728697968</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8288650864355</v>
+        <v>328.8477494193498</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21333,28 +21385,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1153343003551427</v>
+        <v>0.1142108415521847</v>
       </c>
       <c r="J5" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K5" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08915898643684472</v>
+        <v>0.08786773417695593</v>
       </c>
       <c r="M5" t="n">
-        <v>2.169234728696158</v>
+        <v>2.170568152255542</v>
       </c>
       <c r="N5" t="n">
-        <v>7.368649209500624</v>
+        <v>7.362763422532117</v>
       </c>
       <c r="O5" t="n">
-        <v>2.714525595661353</v>
+        <v>2.71344125098225</v>
       </c>
       <c r="P5" t="n">
-        <v>328.1773573330092</v>
+        <v>328.1891441214252</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21415,28 +21467,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1437466790053029</v>
+        <v>-0.1438439302255958</v>
       </c>
       <c r="J6" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K6" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08844000090367754</v>
+        <v>0.08897880826866233</v>
       </c>
       <c r="M6" t="n">
-        <v>2.499226227594282</v>
+        <v>2.493502445432328</v>
       </c>
       <c r="N6" t="n">
-        <v>11.54850101543181</v>
+        <v>11.51921191074887</v>
       </c>
       <c r="O6" t="n">
-        <v>3.398308552122925</v>
+        <v>3.393996451198626</v>
       </c>
       <c r="P6" t="n">
-        <v>328.5936160247999</v>
+        <v>328.5946363377421</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21497,28 +21549,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1625825569815372</v>
+        <v>0.1614830059663838</v>
       </c>
       <c r="J7" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K7" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08725332925081697</v>
+        <v>0.0865333171813496</v>
       </c>
       <c r="M7" t="n">
-        <v>2.922262243851926</v>
+        <v>2.92094660863162</v>
       </c>
       <c r="N7" t="n">
-        <v>14.99372722834165</v>
+        <v>14.96789752943044</v>
       </c>
       <c r="O7" t="n">
-        <v>3.872173450188105</v>
+        <v>3.8688367152712</v>
       </c>
       <c r="P7" t="n">
-        <v>313.2250014798342</v>
+        <v>313.2365374392607</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21575,28 +21627,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04227746906576008</v>
+        <v>0.0420298487011135</v>
       </c>
       <c r="J8" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K8" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008470377086110537</v>
+        <v>0.008416103060832403</v>
       </c>
       <c r="M8" t="n">
-        <v>2.628120069340412</v>
+        <v>2.622770298514912</v>
       </c>
       <c r="N8" t="n">
-        <v>11.34525772167382</v>
+        <v>11.31701431372603</v>
       </c>
       <c r="O8" t="n">
-        <v>3.368272216088513</v>
+        <v>3.364077037424385</v>
       </c>
       <c r="P8" t="n">
-        <v>323.3072810960214</v>
+        <v>323.3098790095701</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21653,28 +21705,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.003611443821309914</v>
+        <v>-0.003823603809394473</v>
       </c>
       <c r="J9" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K9" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L9" t="n">
-        <v>9.278868240736315e-05</v>
+        <v>0.0001045583088806756</v>
       </c>
       <c r="M9" t="n">
-        <v>2.186934688164834</v>
+        <v>2.182269537642563</v>
       </c>
       <c r="N9" t="n">
-        <v>7.62113887768179</v>
+        <v>7.602205428574496</v>
       </c>
       <c r="O9" t="n">
-        <v>2.760641026588171</v>
+        <v>2.757209717916738</v>
       </c>
       <c r="P9" t="n">
-        <v>326.1628644021423</v>
+        <v>326.1650902825069</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21731,28 +21783,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1309146880800837</v>
+        <v>0.1298544770005829</v>
       </c>
       <c r="J10" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K10" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1253746294816822</v>
+        <v>0.1239872983964121</v>
       </c>
       <c r="M10" t="n">
-        <v>2.052681723178016</v>
+        <v>2.052774646903058</v>
       </c>
       <c r="N10" t="n">
-        <v>6.48309842497348</v>
+        <v>6.47805830612286</v>
       </c>
       <c r="O10" t="n">
-        <v>2.546192927681145</v>
+        <v>2.545202999000838</v>
       </c>
       <c r="P10" t="n">
-        <v>323.8596357978944</v>
+        <v>323.8707590216722</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21809,28 +21861,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0650773010024033</v>
+        <v>-0.0667768316913617</v>
       </c>
       <c r="J11" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K11" t="n">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04156520918923912</v>
+        <v>0.04365860387449894</v>
       </c>
       <c r="M11" t="n">
-        <v>1.829476926243809</v>
+        <v>1.833560181891325</v>
       </c>
       <c r="N11" t="n">
-        <v>5.295233568188996</v>
+        <v>5.311198368142933</v>
       </c>
       <c r="O11" t="n">
-        <v>2.301137450955287</v>
+        <v>2.304603733430746</v>
       </c>
       <c r="P11" t="n">
-        <v>329.8205722202866</v>
+        <v>329.8384028773472</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21868,7 +21920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L393"/>
+  <dimension ref="A1:L394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46237,6 +46289,68 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-42.74884003528163,173.39376608459395</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-42.74944248373801,173.39339989402134</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-42.750072170296406,173.39308058217622</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-42.7507133701495,173.39280748161616</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-42.75133081841676,173.3925729475291</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-42.751872139400774,173.39215228930644</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-42.75248385260295,173.3918132211562</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-42.75312002712284,173.39150787074445</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-42.75373182316824,173.39118758445198</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-42.754332929284,173.39083189589934</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L394"/>
+  <dimension ref="A1:L395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16994,6 +16994,48 @@
         <v>324.7</v>
       </c>
       <c r="L394" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>332.2</v>
+      </c>
+      <c r="C395" t="n">
+        <v>332.87</v>
+      </c>
+      <c r="D395" t="n">
+        <v>338.02</v>
+      </c>
+      <c r="E395" t="n">
+        <v>328.16</v>
+      </c>
+      <c r="F395" t="n">
+        <v>324.53</v>
+      </c>
+      <c r="G395" t="n">
+        <v>315.88</v>
+      </c>
+      <c r="H395" t="n">
+        <v>324.37</v>
+      </c>
+      <c r="I395" t="n">
+        <v>325.35</v>
+      </c>
+      <c r="J395" t="n">
+        <v>323.38</v>
+      </c>
+      <c r="K395" t="n">
+        <v>324.78</v>
+      </c>
+      <c r="L395" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17010,7 +17052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B397"/>
+  <dimension ref="A1:B398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20983,6 +21025,16 @@
       </c>
       <c r="B397" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -21151,28 +21203,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7914006359083728</v>
+        <v>0.7896156687769091</v>
       </c>
       <c r="J2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K2" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5543098920297466</v>
+        <v>0.5542635265842299</v>
       </c>
       <c r="M2" t="n">
-        <v>4.377367340225088</v>
+        <v>4.373744600109529</v>
       </c>
       <c r="N2" t="n">
-        <v>27.38236452079129</v>
+        <v>27.34446079423127</v>
       </c>
       <c r="O2" t="n">
-        <v>5.232816117616908</v>
+        <v>5.22919313032434</v>
       </c>
       <c r="P2" t="n">
-        <v>314.8052782644814</v>
+        <v>314.8241894263055</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21229,28 +21281,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7694162096568385</v>
+        <v>0.7673537698139532</v>
       </c>
       <c r="J3" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K3" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4892675952748334</v>
+        <v>0.4889823483436297</v>
       </c>
       <c r="M3" t="n">
-        <v>4.688341921394981</v>
+        <v>4.68508363612464</v>
       </c>
       <c r="N3" t="n">
-        <v>33.60217702795919</v>
+        <v>33.55907321322169</v>
       </c>
       <c r="O3" t="n">
-        <v>5.79673848193613</v>
+        <v>5.793019352049646</v>
       </c>
       <c r="P3" t="n">
-        <v>316.6087316798912</v>
+        <v>316.630582577274</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21307,28 +21359,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4884205656745445</v>
+        <v>0.4865300953304186</v>
       </c>
       <c r="J4" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K4" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3886576086967504</v>
+        <v>0.3877048638238189</v>
       </c>
       <c r="M4" t="n">
-        <v>3.522411135279517</v>
+        <v>3.522733020647085</v>
       </c>
       <c r="N4" t="n">
-        <v>20.40342205927438</v>
+        <v>20.38707666466005</v>
       </c>
       <c r="O4" t="n">
-        <v>4.517014728697968</v>
+        <v>4.51520505233816</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8477494193498</v>
+        <v>328.8677783543208</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21385,28 +21437,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1142108415521847</v>
+        <v>0.1126751632610267</v>
       </c>
       <c r="J5" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K5" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08786773417695593</v>
+        <v>0.08590271280185935</v>
       </c>
       <c r="M5" t="n">
-        <v>2.170568152255542</v>
+        <v>2.174320323964269</v>
       </c>
       <c r="N5" t="n">
-        <v>7.362763422532117</v>
+        <v>7.367462086802429</v>
       </c>
       <c r="O5" t="n">
-        <v>2.71344125098225</v>
+        <v>2.714306925681476</v>
       </c>
       <c r="P5" t="n">
-        <v>328.1891441214252</v>
+        <v>328.205414146885</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21467,28 +21519,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1438439302255958</v>
+        <v>-0.1439759797107827</v>
       </c>
       <c r="J6" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K6" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08897880826866233</v>
+        <v>0.08957270677430473</v>
       </c>
       <c r="M6" t="n">
-        <v>2.493502445432328</v>
+        <v>2.488018378562646</v>
       </c>
       <c r="N6" t="n">
-        <v>11.51921191074887</v>
+        <v>11.49014824490735</v>
       </c>
       <c r="O6" t="n">
-        <v>3.393996451198626</v>
+        <v>3.389712118293728</v>
       </c>
       <c r="P6" t="n">
-        <v>328.5946363377421</v>
+        <v>328.5960353602446</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21549,28 +21601,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1614830059663838</v>
+        <v>0.16066377927005</v>
       </c>
       <c r="J7" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K7" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0865333171813496</v>
+        <v>0.08612841018485773</v>
       </c>
       <c r="M7" t="n">
-        <v>2.92094660863162</v>
+        <v>2.917999373386418</v>
       </c>
       <c r="N7" t="n">
-        <v>14.96789752943044</v>
+        <v>14.93656314682266</v>
       </c>
       <c r="O7" t="n">
-        <v>3.8688367152712</v>
+        <v>3.864785006545987</v>
       </c>
       <c r="P7" t="n">
-        <v>313.2365374392607</v>
+        <v>313.2452168868269</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21627,28 +21679,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0420298487011135</v>
+        <v>0.04200144262365578</v>
       </c>
       <c r="J8" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K8" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008416103060832403</v>
+        <v>0.008450652102428458</v>
       </c>
       <c r="M8" t="n">
-        <v>2.622770298514912</v>
+        <v>2.616263774605128</v>
       </c>
       <c r="N8" t="n">
-        <v>11.31701431372603</v>
+        <v>11.28829892872351</v>
       </c>
       <c r="O8" t="n">
-        <v>3.364077037424385</v>
+        <v>3.359806382624378</v>
       </c>
       <c r="P8" t="n">
-        <v>323.3098790095701</v>
+        <v>323.3101799629703</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21705,28 +21757,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.003823603809394473</v>
+        <v>-0.004181660225967687</v>
       </c>
       <c r="J9" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K9" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001045583088806756</v>
+        <v>0.0001257216641969983</v>
       </c>
       <c r="M9" t="n">
-        <v>2.182269537642563</v>
+        <v>2.178211917185096</v>
       </c>
       <c r="N9" t="n">
-        <v>7.602205428574496</v>
+        <v>7.584181814713472</v>
       </c>
       <c r="O9" t="n">
-        <v>2.757209717916738</v>
+        <v>2.75393932662168</v>
       </c>
       <c r="P9" t="n">
-        <v>326.1650902825069</v>
+        <v>326.1688837769172</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21783,28 +21835,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1298544770005829</v>
+        <v>0.1278765147467662</v>
       </c>
       <c r="J10" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K10" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1239872983964121</v>
+        <v>0.1206380468889722</v>
       </c>
       <c r="M10" t="n">
-        <v>2.052774646903058</v>
+        <v>2.057265512586306</v>
       </c>
       <c r="N10" t="n">
-        <v>6.47805830612286</v>
+        <v>6.500412738817405</v>
       </c>
       <c r="O10" t="n">
-        <v>2.545202999000838</v>
+        <v>2.549590700253161</v>
       </c>
       <c r="P10" t="n">
-        <v>323.8707590216722</v>
+        <v>323.8917149057355</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21861,28 +21913,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0667768316913617</v>
+        <v>-0.06843597448641701</v>
       </c>
       <c r="J11" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K11" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04365860387449894</v>
+        <v>0.04576961407966296</v>
       </c>
       <c r="M11" t="n">
-        <v>1.833560181891325</v>
+        <v>1.837244728424686</v>
       </c>
       <c r="N11" t="n">
-        <v>5.311198368142933</v>
+        <v>5.325015537439986</v>
       </c>
       <c r="O11" t="n">
-        <v>2.304603733430746</v>
+        <v>2.307599518426017</v>
       </c>
       <c r="P11" t="n">
-        <v>329.8384028773472</v>
+        <v>329.8559809701499</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21920,7 +21972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L394"/>
+  <dimension ref="A1:L395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46351,6 +46403,68 @@
         </is>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:46+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-42.74884540867597,173.39378182923858</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-42.74944554886192,173.39340887519657</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-42.750072008078135,173.39307988285046</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-42.750712006550245,173.39279800739317</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-42.75133055705532,173.39257177818797</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-42.75187444456427,173.39215892028116</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-42.752485537452216,173.39181822217824</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-42.75311911420958,173.39150455059448</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-42.75372589827965,173.39116737352913</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-42.7543332098985,173.39083279628738</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L395"/>
+  <dimension ref="A1:L397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17036,6 +17036,90 @@
         <v>324.78</v>
       </c>
       <c r="L395" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>331.51</v>
+      </c>
+      <c r="C396" t="n">
+        <v>332.73</v>
+      </c>
+      <c r="D396" t="n">
+        <v>338</v>
+      </c>
+      <c r="E396" t="n">
+        <v>327.98</v>
+      </c>
+      <c r="F396" t="n">
+        <v>324.69</v>
+      </c>
+      <c r="G396" t="n">
+        <v>315.72</v>
+      </c>
+      <c r="H396" t="n">
+        <v>323.62</v>
+      </c>
+      <c r="I396" t="n">
+        <v>324.57</v>
+      </c>
+      <c r="J396" t="n">
+        <v>323.89</v>
+      </c>
+      <c r="K396" t="n">
+        <v>324.72</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="C397" t="n">
+        <v>333.14</v>
+      </c>
+      <c r="D397" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="E397" t="n">
+        <v>328.96</v>
+      </c>
+      <c r="F397" t="n">
+        <v>323.94</v>
+      </c>
+      <c r="G397" t="n">
+        <v>315.46</v>
+      </c>
+      <c r="H397" t="n">
+        <v>323.81</v>
+      </c>
+      <c r="I397" t="n">
+        <v>323.44</v>
+      </c>
+      <c r="J397" t="n">
+        <v>323.66</v>
+      </c>
+      <c r="K397" t="n">
+        <v>325.7</v>
+      </c>
+      <c r="L397" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17052,7 +17136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B398"/>
+  <dimension ref="A1:B400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21035,6 +21119,26 @@
       </c>
       <c r="B398" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -21203,28 +21307,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7896156687769091</v>
+        <v>0.7844631345587221</v>
       </c>
       <c r="J2" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K2" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5542635265842299</v>
+        <v>0.5524893318748841</v>
       </c>
       <c r="M2" t="n">
-        <v>4.373744600109529</v>
+        <v>4.373002198785973</v>
       </c>
       <c r="N2" t="n">
-        <v>27.34446079423127</v>
+        <v>27.34309441588768</v>
       </c>
       <c r="O2" t="n">
-        <v>5.22919313032434</v>
+        <v>5.229062479631285</v>
       </c>
       <c r="P2" t="n">
-        <v>314.8241894263055</v>
+        <v>314.8789448676255</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21281,28 +21385,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7673537698139532</v>
+        <v>0.7633180975672277</v>
       </c>
       <c r="J3" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K3" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4889823483436297</v>
+        <v>0.4884686242407048</v>
       </c>
       <c r="M3" t="n">
-        <v>4.68508363612464</v>
+        <v>4.678373744934528</v>
       </c>
       <c r="N3" t="n">
-        <v>33.55907321322169</v>
+        <v>33.47108652944256</v>
       </c>
       <c r="O3" t="n">
-        <v>5.793019352049646</v>
+        <v>5.785420168790038</v>
       </c>
       <c r="P3" t="n">
-        <v>316.630582577274</v>
+        <v>316.6734599412193</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21359,28 +21463,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4865300953304186</v>
+        <v>0.4828559098207441</v>
       </c>
       <c r="J4" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K4" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3877048638238189</v>
+        <v>0.3859136915515758</v>
       </c>
       <c r="M4" t="n">
-        <v>3.522733020647085</v>
+        <v>3.522753581909236</v>
       </c>
       <c r="N4" t="n">
-        <v>20.38707666466005</v>
+        <v>20.35154656980944</v>
       </c>
       <c r="O4" t="n">
-        <v>4.51520505233816</v>
+        <v>4.511268842555213</v>
       </c>
       <c r="P4" t="n">
-        <v>328.8677783543208</v>
+        <v>328.9068159803742</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21437,28 +21541,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1126751632610267</v>
+        <v>0.1099611374915014</v>
       </c>
       <c r="J5" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K5" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08590271280185935</v>
+        <v>0.08258519236089357</v>
       </c>
       <c r="M5" t="n">
-        <v>2.174320323964269</v>
+        <v>2.179924380314186</v>
       </c>
       <c r="N5" t="n">
-        <v>7.367462086802429</v>
+        <v>7.368262615053066</v>
       </c>
       <c r="O5" t="n">
-        <v>2.714306925681476</v>
+        <v>2.714454386253905</v>
       </c>
       <c r="P5" t="n">
-        <v>328.205414146885</v>
+        <v>328.2342458599938</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21519,28 +21623,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1439759797107827</v>
+        <v>-0.1444419756400911</v>
       </c>
       <c r="J6" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K6" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08957270677430473</v>
+        <v>0.09098823496153108</v>
       </c>
       <c r="M6" t="n">
-        <v>2.488018378562646</v>
+        <v>2.478396980058573</v>
       </c>
       <c r="N6" t="n">
-        <v>11.49014824490735</v>
+        <v>11.43389478665663</v>
       </c>
       <c r="O6" t="n">
-        <v>3.389712118293728</v>
+        <v>3.381404262530085</v>
       </c>
       <c r="P6" t="n">
-        <v>328.5960353602446</v>
+        <v>328.6009903907507</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21601,28 +21705,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.16066377927005</v>
+        <v>0.1587498301903691</v>
       </c>
       <c r="J7" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K7" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08612841018485773</v>
+        <v>0.08501137202344244</v>
       </c>
       <c r="M7" t="n">
-        <v>2.917999373386418</v>
+        <v>2.913716049150764</v>
       </c>
       <c r="N7" t="n">
-        <v>14.93656314682266</v>
+        <v>14.87949862855392</v>
       </c>
       <c r="O7" t="n">
-        <v>3.864785006545987</v>
+        <v>3.85739531660341</v>
       </c>
       <c r="P7" t="n">
-        <v>313.2452168868269</v>
+        <v>313.2655540901105</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21679,28 +21783,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04200144262365578</v>
+        <v>0.04129575409286224</v>
       </c>
       <c r="J8" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K8" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008450652102428458</v>
+        <v>0.008258570454587888</v>
       </c>
       <c r="M8" t="n">
-        <v>2.616263774605128</v>
+        <v>2.606744756597228</v>
       </c>
       <c r="N8" t="n">
-        <v>11.28829892872351</v>
+        <v>11.23382018359522</v>
       </c>
       <c r="O8" t="n">
-        <v>3.359806382624378</v>
+        <v>3.351689153784285</v>
       </c>
       <c r="P8" t="n">
-        <v>323.3101799629703</v>
+        <v>323.3176769844545</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21757,28 +21861,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.004181660225967687</v>
+        <v>-0.006230296072158002</v>
       </c>
       <c r="J9" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K9" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001257216641969983</v>
+        <v>0.0002812626323280831</v>
       </c>
       <c r="M9" t="n">
-        <v>2.178211917185096</v>
+        <v>2.17565901215513</v>
       </c>
       <c r="N9" t="n">
-        <v>7.584181814713472</v>
+        <v>7.568437933138903</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75393932662168</v>
+        <v>2.751079412365064</v>
       </c>
       <c r="P9" t="n">
-        <v>326.1688837769172</v>
+        <v>326.1906564742513</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21835,28 +21939,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1278765147467662</v>
+        <v>0.1243784134831624</v>
       </c>
       <c r="J10" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K10" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1206380468889722</v>
+        <v>0.1150303929057583</v>
       </c>
       <c r="M10" t="n">
-        <v>2.057265512586306</v>
+        <v>2.064335498688598</v>
       </c>
       <c r="N10" t="n">
-        <v>6.500412738817405</v>
+        <v>6.528732371032282</v>
       </c>
       <c r="O10" t="n">
-        <v>2.549590700253161</v>
+        <v>2.555138425023639</v>
       </c>
       <c r="P10" t="n">
-        <v>323.8917149057355</v>
+        <v>323.9288836652643</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21913,28 +22017,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06843597448641701</v>
+        <v>-0.07126015650408912</v>
       </c>
       <c r="J11" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K11" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04576961407966296</v>
+        <v>0.04958550044572119</v>
       </c>
       <c r="M11" t="n">
-        <v>1.837244728424686</v>
+        <v>1.84229474028287</v>
       </c>
       <c r="N11" t="n">
-        <v>5.325015537439986</v>
+        <v>5.339185183242853</v>
       </c>
       <c r="O11" t="n">
-        <v>2.307599518426017</v>
+        <v>2.310667692084444</v>
       </c>
       <c r="P11" t="n">
-        <v>329.8559809701499</v>
+        <v>329.885983086658</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21972,7 +22076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L395"/>
+  <dimension ref="A1:L397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46465,6 +46569,130 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:43+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-42.74884279766067,173.3937741786715</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-42.749445019087474,173.3934073228946</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-42.75007195400538,173.39307964974185</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-42.750711695856644,173.3927958487095</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-42.751330975233614,173.3925736491338</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-42.75187382985405,173.39215715202118</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-42.75248272936998,173.39180988714168</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-42.75311665878723,173.39149562053638</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-42.75372759586045,173.39117316429878</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-42.75433299943762,173.39083212099635</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-42.74883594847323,173.39375410979562</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-42.749446570569745,173.39341186892182</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-42.750072440660176,173.3930817477192</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-42.75071338741023,173.392807601543</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-42.75132901502259,173.3925648790754</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-42.75187283094988,173.3921542785988</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-42.75248344075087,173.3918119986842</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-42.75311310157156,173.3914826834022</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-42.753726830284826,173.39117055277515</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>-42.754336436964806,173.3908431507503</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L397"/>
+  <dimension ref="A1:L400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17120,6 +17120,132 @@
         <v>325.7</v>
       </c>
       <c r="L397" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>328.6</v>
+      </c>
+      <c r="C398" t="n">
+        <v>332.7</v>
+      </c>
+      <c r="D398" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="E398" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="F398" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="G398" t="n">
+        <v>315.19</v>
+      </c>
+      <c r="H398" t="n">
+        <v>322.67</v>
+      </c>
+      <c r="I398" t="n">
+        <v>322.91</v>
+      </c>
+      <c r="J398" t="n">
+        <v>322.9</v>
+      </c>
+      <c r="K398" t="n">
+        <v>325.41</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>328.42</v>
+      </c>
+      <c r="C399" t="n">
+        <v>332.08</v>
+      </c>
+      <c r="D399" t="n">
+        <v>336.46</v>
+      </c>
+      <c r="E399" t="n">
+        <v>328.52</v>
+      </c>
+      <c r="F399" t="n">
+        <v>323.45</v>
+      </c>
+      <c r="G399" t="n">
+        <v>314.92</v>
+      </c>
+      <c r="H399" t="n">
+        <v>321.68</v>
+      </c>
+      <c r="I399" t="n">
+        <v>322.48</v>
+      </c>
+      <c r="J399" t="n">
+        <v>322.71</v>
+      </c>
+      <c r="K399" t="n">
+        <v>324.86</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="C400" t="n">
+        <v>331.06</v>
+      </c>
+      <c r="D400" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="E400" t="n">
+        <v>327.4</v>
+      </c>
+      <c r="F400" t="n">
+        <v>322.41</v>
+      </c>
+      <c r="G400" t="n">
+        <v>314.95</v>
+      </c>
+      <c r="H400" t="n">
+        <v>319.67</v>
+      </c>
+      <c r="I400" t="n">
+        <v>321.16</v>
+      </c>
+      <c r="J400" t="n">
+        <v>322.16</v>
+      </c>
+      <c r="K400" t="n">
+        <v>324.75</v>
+      </c>
+      <c r="L400" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17136,7 +17262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B400"/>
+  <dimension ref="A1:B403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21139,6 +21265,36 @@
       </c>
       <c r="B400" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -21307,28 +21463,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7844631345587221</v>
+        <v>0.7735975710982043</v>
       </c>
       <c r="J2" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5524893318748841</v>
+        <v>0.545981765055138</v>
       </c>
       <c r="M2" t="n">
-        <v>4.373002198785973</v>
+        <v>4.385648609257945</v>
       </c>
       <c r="N2" t="n">
-        <v>27.34309441588768</v>
+        <v>27.53710960437545</v>
       </c>
       <c r="O2" t="n">
-        <v>5.229062479631285</v>
+        <v>5.247581309934649</v>
       </c>
       <c r="P2" t="n">
-        <v>314.8789448676255</v>
+        <v>314.9948358215051</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21385,28 +21541,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7633180975672277</v>
+        <v>0.7558892838247057</v>
       </c>
       <c r="J3" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K3" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4884686242407048</v>
+        <v>0.4862103183571455</v>
       </c>
       <c r="M3" t="n">
-        <v>4.678373744934528</v>
+        <v>4.674261326422601</v>
       </c>
       <c r="N3" t="n">
-        <v>33.47108652944256</v>
+        <v>33.40954677756711</v>
       </c>
       <c r="O3" t="n">
-        <v>5.785420168790038</v>
+        <v>5.780099201360398</v>
       </c>
       <c r="P3" t="n">
-        <v>316.6734599412193</v>
+        <v>316.7527015711681</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21463,28 +21619,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4828559098207441</v>
+        <v>0.4746219866069702</v>
       </c>
       <c r="J4" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K4" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3859136915515758</v>
+        <v>0.3789478371685377</v>
       </c>
       <c r="M4" t="n">
-        <v>3.522753581909236</v>
+        <v>3.536543639284912</v>
       </c>
       <c r="N4" t="n">
-        <v>20.35154656980944</v>
+        <v>20.42854106118588</v>
       </c>
       <c r="O4" t="n">
-        <v>4.511268842555213</v>
+        <v>4.519794360497597</v>
       </c>
       <c r="P4" t="n">
-        <v>328.9068159803742</v>
+        <v>328.9946391471645</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21541,28 +21697,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1099611374915014</v>
+        <v>0.1053138147028823</v>
       </c>
       <c r="J5" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K5" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08258519236089357</v>
+        <v>0.07670201674790822</v>
       </c>
       <c r="M5" t="n">
-        <v>2.179924380314186</v>
+        <v>2.192200410368493</v>
       </c>
       <c r="N5" t="n">
-        <v>7.368262615053066</v>
+        <v>7.387522090524598</v>
       </c>
       <c r="O5" t="n">
-        <v>2.714454386253905</v>
+        <v>2.717999648735187</v>
       </c>
       <c r="P5" t="n">
-        <v>328.2342458599938</v>
+        <v>328.283816219341</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21623,28 +21779,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1444419756400911</v>
+        <v>-0.1468577664523064</v>
       </c>
       <c r="J6" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K6" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09098823496153108</v>
+        <v>0.09499391722408357</v>
       </c>
       <c r="M6" t="n">
-        <v>2.478396980058573</v>
+        <v>2.474813182102807</v>
       </c>
       <c r="N6" t="n">
-        <v>11.43389478665663</v>
+        <v>11.36953071556995</v>
       </c>
       <c r="O6" t="n">
-        <v>3.381404262530085</v>
+        <v>3.371873472651362</v>
       </c>
       <c r="P6" t="n">
-        <v>328.6009903907507</v>
+        <v>328.6267618934016</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21705,28 +21861,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1587498301903691</v>
+        <v>0.1551128448014423</v>
       </c>
       <c r="J7" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K7" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08501137202344244</v>
+        <v>0.08246745473346395</v>
       </c>
       <c r="M7" t="n">
-        <v>2.913716049150764</v>
+        <v>2.911877675467712</v>
       </c>
       <c r="N7" t="n">
-        <v>14.87949862855392</v>
+        <v>14.81246759887238</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85739531660341</v>
+        <v>3.848696870224047</v>
       </c>
       <c r="P7" t="n">
-        <v>313.2655540901105</v>
+        <v>313.3043461717921</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21783,28 +21939,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04129575409286224</v>
+        <v>0.03675815737533442</v>
       </c>
       <c r="J8" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K8" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008258570454587888</v>
+        <v>0.006613250438236351</v>
       </c>
       <c r="M8" t="n">
-        <v>2.606744756597228</v>
+        <v>2.611140424819759</v>
       </c>
       <c r="N8" t="n">
-        <v>11.23382018359522</v>
+        <v>11.23062327719818</v>
       </c>
       <c r="O8" t="n">
-        <v>3.351689153784285</v>
+        <v>3.351212210111167</v>
       </c>
       <c r="P8" t="n">
-        <v>323.3176769844545</v>
+        <v>323.3660886366568</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -21861,28 +22017,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.006230296072158002</v>
+        <v>-0.0118856903399644</v>
       </c>
       <c r="J9" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K9" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002812626323280831</v>
+        <v>0.001024294242812918</v>
       </c>
       <c r="M9" t="n">
-        <v>2.17565901215513</v>
+        <v>2.183095660270542</v>
       </c>
       <c r="N9" t="n">
-        <v>7.568437933138903</v>
+        <v>7.623809186733503</v>
       </c>
       <c r="O9" t="n">
-        <v>2.751079412365064</v>
+        <v>2.761124623542643</v>
       </c>
       <c r="P9" t="n">
-        <v>326.1906564742513</v>
+        <v>326.2509838369701</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -21939,28 +22095,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1243784134831624</v>
+        <v>0.1175312178845398</v>
       </c>
       <c r="J10" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K10" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1150303929057583</v>
+        <v>0.1032461576284378</v>
       </c>
       <c r="M10" t="n">
-        <v>2.064335498688598</v>
+        <v>2.083381243166495</v>
       </c>
       <c r="N10" t="n">
-        <v>6.528732371032282</v>
+        <v>6.638941187285063</v>
       </c>
       <c r="O10" t="n">
-        <v>2.555138425023639</v>
+        <v>2.57661428764281</v>
       </c>
       <c r="P10" t="n">
-        <v>323.9288836652643</v>
+        <v>324.0019173054121</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22017,28 +22173,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07126015650408912</v>
+        <v>-0.07565479287237876</v>
       </c>
       <c r="J11" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K11" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04958550044572119</v>
+        <v>0.05574297174382514</v>
       </c>
       <c r="M11" t="n">
-        <v>1.84229474028287</v>
+        <v>1.850548000556566</v>
       </c>
       <c r="N11" t="n">
-        <v>5.339185183242853</v>
+        <v>5.36495398889262</v>
       </c>
       <c r="O11" t="n">
-        <v>2.310667692084444</v>
+        <v>2.316237032104577</v>
       </c>
       <c r="P11" t="n">
-        <v>329.885983086658</v>
+        <v>329.9328580716548</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22076,7 +22232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L397"/>
+  <dimension ref="A1:L400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46693,6 +46849,192 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-42.748831785981885,173.3937419132434</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-42.74944490556437,173.39340699025848</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-42.75006738485571,173.39305995206703</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-42.750711902985714,173.3927972878319</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>-42.75132786503181,173.3925597339747</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>-42.751871793626215,173.39215129466027</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-42.75247917246492,173.39179932942974</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-42.75311143314245,173.3914766155433</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>-42.753724300556264,173.3911619233933</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>-42.75433541973749,173.3908398868434</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>-42.74883110484682,173.3937399174441</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>-42.74944255942009,173.39340011577875</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>-42.75006779040169,173.39306170038125</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-42.75071262793735,173.39280232476054</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>-42.75132773435102,173.39255914930422</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>-42.75187075630249,173.39214831072184</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>-42.7524754657944,173.39178832718383</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>-42.75311007951106,173.3914716925637</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>-42.753723668124024,173.39115976604793</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>-42.754333490513,173.3908336966754</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-42.748829969621625,173.393736591112</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-42.74943869963343,173.3933888061519</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-42.7500658437808,173.39305330847324</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-42.75071069473252,173.39278889295116</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>-42.75132501619001,173.392546988158</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>-42.751870871560676,173.39214864227054</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-42.75246794012675,173.39176598929467</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-42.75310592417616,173.39145658016247</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>-42.75372183739888,173.39115352110107</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>-42.754333104668056,173.39083245864185</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L400"/>
+  <dimension ref="A1:L402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17246,6 +17246,90 @@
         <v>324.75</v>
       </c>
       <c r="L400" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>328.46</v>
+      </c>
+      <c r="C401" t="n">
+        <v>331.08</v>
+      </c>
+      <c r="D401" t="n">
+        <v>335.68</v>
+      </c>
+      <c r="E401" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="F401" t="n">
+        <v>322.54</v>
+      </c>
+      <c r="G401" t="n">
+        <v>315.69</v>
+      </c>
+      <c r="H401" t="n">
+        <v>319.98</v>
+      </c>
+      <c r="I401" t="n">
+        <v>320.97</v>
+      </c>
+      <c r="J401" t="n">
+        <v>322.27</v>
+      </c>
+      <c r="K401" t="n">
+        <v>323.64</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>328.14</v>
+      </c>
+      <c r="C402" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="D402" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="E402" t="n">
+        <v>327.81</v>
+      </c>
+      <c r="F402" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="G402" t="n">
+        <v>314.76</v>
+      </c>
+      <c r="H402" t="n">
+        <v>318.45</v>
+      </c>
+      <c r="I402" t="n">
+        <v>320.19</v>
+      </c>
+      <c r="J402" t="n">
+        <v>322.67</v>
+      </c>
+      <c r="K402" t="n">
+        <v>323.22</v>
+      </c>
+      <c r="L402" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17262,7 +17346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B403"/>
+  <dimension ref="A1:B405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21295,6 +21379,26 @@
       </c>
       <c r="B403" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>
@@ -21463,28 +21567,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7735975710982043</v>
+        <v>0.7664793251782342</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K2" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L2" t="n">
-        <v>0.545981765055138</v>
+        <v>0.5416621577832101</v>
       </c>
       <c r="M2" t="n">
-        <v>4.385648609257945</v>
+        <v>4.394136130621942</v>
       </c>
       <c r="N2" t="n">
-        <v>27.53710960437545</v>
+        <v>27.66329491799916</v>
       </c>
       <c r="O2" t="n">
-        <v>5.247581309934649</v>
+        <v>5.259590755752691</v>
       </c>
       <c r="P2" t="n">
-        <v>314.9948358215051</v>
+        <v>315.0709399569536</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21541,28 +21645,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7558892838247057</v>
+        <v>0.7499894858936412</v>
       </c>
       <c r="J3" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K3" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4862103183571455</v>
+        <v>0.483597462760855</v>
       </c>
       <c r="M3" t="n">
-        <v>4.674261326422601</v>
+        <v>4.675615752399134</v>
       </c>
       <c r="N3" t="n">
-        <v>33.40954677756711</v>
+        <v>33.4241599339155</v>
       </c>
       <c r="O3" t="n">
-        <v>5.780099201360398</v>
+        <v>5.781363155339362</v>
       </c>
       <c r="P3" t="n">
-        <v>316.7527015711681</v>
+        <v>316.8157793416001</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21619,28 +21723,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4746219866069702</v>
+        <v>0.4691111205486151</v>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K4" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3789478371685377</v>
+        <v>0.3741424952514727</v>
       </c>
       <c r="M4" t="n">
-        <v>3.536543639284912</v>
+        <v>3.547274674230515</v>
       </c>
       <c r="N4" t="n">
-        <v>20.42854106118588</v>
+        <v>20.48498636954081</v>
       </c>
       <c r="O4" t="n">
-        <v>4.519794360497597</v>
+        <v>4.526034287269685</v>
       </c>
       <c r="P4" t="n">
-        <v>328.9946391471645</v>
+        <v>329.0535559669437</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21697,28 +21801,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1053138147028823</v>
+        <v>0.1018742201114614</v>
       </c>
       <c r="J5" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K5" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07670201674790822</v>
+        <v>0.07228117548838209</v>
       </c>
       <c r="M5" t="n">
-        <v>2.192200410368493</v>
+        <v>2.202884144897927</v>
       </c>
       <c r="N5" t="n">
-        <v>7.387522090524598</v>
+        <v>7.412514454051483</v>
       </c>
       <c r="O5" t="n">
-        <v>2.717999648735187</v>
+        <v>2.7225933324776</v>
       </c>
       <c r="P5" t="n">
-        <v>328.283816219341</v>
+        <v>328.3205886649183</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21779,28 +21883,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1468577664523064</v>
+        <v>-0.1489623960258163</v>
       </c>
       <c r="J6" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K6" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09499391722408357</v>
+        <v>0.09822930109921479</v>
       </c>
       <c r="M6" t="n">
-        <v>2.474813182102807</v>
+        <v>2.475633023006639</v>
       </c>
       <c r="N6" t="n">
-        <v>11.36953071556995</v>
+        <v>11.33585183775853</v>
       </c>
       <c r="O6" t="n">
-        <v>3.371873472651362</v>
+        <v>3.366875678987647</v>
       </c>
       <c r="P6" t="n">
-        <v>328.6267618934016</v>
+        <v>328.6492630681278</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21861,28 +21965,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1551128448014423</v>
+        <v>0.1529574022822728</v>
       </c>
       <c r="J7" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K7" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08246745473346395</v>
+        <v>0.08103744079813902</v>
       </c>
       <c r="M7" t="n">
-        <v>2.911877675467712</v>
+        <v>2.909201204226575</v>
       </c>
       <c r="N7" t="n">
-        <v>14.81246759887238</v>
+        <v>14.76382523046403</v>
       </c>
       <c r="O7" t="n">
-        <v>3.848696870224047</v>
+        <v>3.842372344068704</v>
       </c>
       <c r="P7" t="n">
-        <v>313.3043461717921</v>
+        <v>313.3273930122457</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -21939,28 +22043,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03675815737533442</v>
+        <v>0.03176828225279255</v>
       </c>
       <c r="J8" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K8" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006613250438236351</v>
+        <v>0.004942395670573307</v>
       </c>
       <c r="M8" t="n">
-        <v>2.611140424819759</v>
+        <v>2.625535658786814</v>
       </c>
       <c r="N8" t="n">
-        <v>11.23062327719818</v>
+        <v>11.30691102294974</v>
       </c>
       <c r="O8" t="n">
-        <v>3.351212210111167</v>
+        <v>3.362575058336949</v>
       </c>
       <c r="P8" t="n">
-        <v>323.3660886366568</v>
+        <v>323.4194407296109</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22017,28 +22121,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0118856903399644</v>
+        <v>-0.01708841701313423</v>
       </c>
       <c r="J9" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K9" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001024294242812918</v>
+        <v>0.002098522797829738</v>
       </c>
       <c r="M9" t="n">
-        <v>2.183095660270542</v>
+        <v>2.194114474222119</v>
       </c>
       <c r="N9" t="n">
-        <v>7.623809186733503</v>
+        <v>7.727222863505742</v>
       </c>
       <c r="O9" t="n">
-        <v>2.761124623542643</v>
+        <v>2.779788276740828</v>
       </c>
       <c r="P9" t="n">
-        <v>326.2509838369701</v>
+        <v>326.3066096923508</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22095,28 +22199,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1175312178845398</v>
+        <v>0.1129971204868018</v>
       </c>
       <c r="J10" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K10" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1032461576284378</v>
+        <v>0.09571414739156303</v>
       </c>
       <c r="M10" t="n">
-        <v>2.083381243166495</v>
+        <v>2.096232884288291</v>
       </c>
       <c r="N10" t="n">
-        <v>6.638941187285063</v>
+        <v>6.712899589718448</v>
       </c>
       <c r="O10" t="n">
-        <v>2.57661428764281</v>
+        <v>2.590926396044173</v>
       </c>
       <c r="P10" t="n">
-        <v>324.0019173054121</v>
+        <v>324.0503917110419</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22173,28 +22277,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07565479287237876</v>
+        <v>-0.08001260497048374</v>
       </c>
       <c r="J11" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K11" t="n">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05574297174382514</v>
+        <v>0.06149365958532449</v>
       </c>
       <c r="M11" t="n">
-        <v>1.850548000556566</v>
+        <v>1.863084772871162</v>
       </c>
       <c r="N11" t="n">
-        <v>5.36495398889262</v>
+        <v>5.437127138350439</v>
       </c>
       <c r="O11" t="n">
-        <v>2.316237032104577</v>
+        <v>2.331764811971919</v>
       </c>
       <c r="P11" t="n">
-        <v>329.9328580716548</v>
+        <v>329.9794498017637</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22232,7 +22336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L400"/>
+  <dimension ref="A1:L402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47035,6 +47139,130 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-42.74883125621017,173.39374036095504</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-42.74943877531554,173.39338902790925</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-42.75006568156236,173.39305260914762</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>-42.75071052212487,173.3927876936825</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>-42.75132535596021,173.3925485083012</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>-42.751873714595874,173.39215682047245</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>-42.75246910080215,173.39176943444141</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>-42.753105326059604,173.39145440489276</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>-42.75372220354394,173.39115477009042</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>-42.75432921114112,173.3908199657587</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:07:10+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-42.7488300453033,173.39373681286747</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-42.74943695894497,173.39338370573242</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-42.75006730374653,173.3930596024042</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-42.750711402423754,173.3927938099527</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>-42.751325382096375,173.3925486252353</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>-42.751870141592086,173.39214654246206</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>-42.752463372306444,173.3917524309765</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>-42.75310287063333,173.3914454748386</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>-42.75372353498039,173.39115931186996</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>-42.75432773791436,173.3908152387222</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0401/nzd0401.xlsx
+++ b/data/nzd0401/nzd0401.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L402"/>
+  <dimension ref="A1:L403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17330,6 +17330,48 @@
         <v>323.22</v>
       </c>
       <c r="L402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="C403" t="n">
+        <v>330.28</v>
+      </c>
+      <c r="D403" t="n">
+        <v>336.2</v>
+      </c>
+      <c r="E403" t="n">
+        <v>326.84</v>
+      </c>
+      <c r="F403" t="n">
+        <v>322.65</v>
+      </c>
+      <c r="G403" t="n">
+        <v>314.74</v>
+      </c>
+      <c r="H403" t="n">
+        <v>317.97</v>
+      </c>
+      <c r="I403" t="n">
+        <v>319.8</v>
+      </c>
+      <c r="J403" t="n">
+        <v>322.39</v>
+      </c>
+      <c r="K403" t="n">
+        <v>322.47</v>
+      </c>
+      <c r="L403" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -17346,7 +17388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B405"/>
+  <dimension ref="A1:B406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21399,6 +21441,16 @@
       </c>
       <c r="B405" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B406" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -21567,28 +21619,28 @@
         <v>0.1636</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7664793251782342</v>
+        <v>0.7625944802278545</v>
       </c>
       <c r="J2" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K2" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5416621577832101</v>
+        <v>0.5390514531506083</v>
       </c>
       <c r="M2" t="n">
-        <v>4.394136130621942</v>
+        <v>4.400280352738379</v>
       </c>
       <c r="N2" t="n">
-        <v>27.66329491799916</v>
+        <v>27.75184451739481</v>
       </c>
       <c r="O2" t="n">
-        <v>5.259590755752691</v>
+        <v>5.268001947360575</v>
       </c>
       <c r="P2" t="n">
-        <v>315.0709399569536</v>
+        <v>315.1126535800467</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21645,28 +21697,28 @@
         <v>0.1733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7499894858936412</v>
+        <v>0.7467738142169779</v>
       </c>
       <c r="J3" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K3" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L3" t="n">
-        <v>0.483597462760855</v>
+        <v>0.4819782624026103</v>
       </c>
       <c r="M3" t="n">
-        <v>4.675615752399134</v>
+        <v>4.677264595497669</v>
       </c>
       <c r="N3" t="n">
-        <v>33.4241599339155</v>
+        <v>33.44883561325486</v>
       </c>
       <c r="O3" t="n">
-        <v>5.781363155339362</v>
+        <v>5.783496832648468</v>
       </c>
       <c r="P3" t="n">
-        <v>316.8157793416001</v>
+        <v>316.8503076993659</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21723,28 +21775,28 @@
         <v>0.1687</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4691111205486151</v>
+        <v>0.4664792818184871</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3741424952514727</v>
+        <v>0.3719340792207591</v>
       </c>
       <c r="M4" t="n">
-        <v>3.547274674230515</v>
+        <v>3.552328624807051</v>
       </c>
       <c r="N4" t="n">
-        <v>20.48498636954081</v>
+        <v>20.50625175569139</v>
       </c>
       <c r="O4" t="n">
-        <v>4.526034287269685</v>
+        <v>4.528382907362339</v>
       </c>
       <c r="P4" t="n">
-        <v>329.0535559669437</v>
+        <v>329.0818154033518</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -21801,28 +21853,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1018742201114614</v>
+        <v>0.0998283415003499</v>
       </c>
       <c r="J5" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K5" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07228117548838209</v>
+        <v>0.06957178550478094</v>
       </c>
       <c r="M5" t="n">
-        <v>2.202884144897927</v>
+        <v>2.210233563465528</v>
       </c>
       <c r="N5" t="n">
-        <v>7.412514454051483</v>
+        <v>7.43771861334915</v>
       </c>
       <c r="O5" t="n">
-        <v>2.7225933324776</v>
+        <v>2.727218108870127</v>
       </c>
       <c r="P5" t="n">
-        <v>328.3205886649183</v>
+        <v>328.342556339399</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21883,28 +21935,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1489623960258163</v>
+        <v>-0.1499419539335279</v>
       </c>
       <c r="J6" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K6" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09822930109921479</v>
+        <v>0.09979597337105972</v>
       </c>
       <c r="M6" t="n">
-        <v>2.475633023006639</v>
+        <v>2.475583982326831</v>
       </c>
       <c r="N6" t="n">
-        <v>11.33585183775853</v>
+        <v>11.31765821278653</v>
       </c>
       <c r="O6" t="n">
-        <v>3.366875678987647</v>
+        <v>3.364172738250301</v>
       </c>
       <c r="P6" t="n">
-        <v>328.6492630681278</v>
+        <v>328.6597810964872</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21965,28 +22017,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1529574022822728</v>
+        <v>0.1516512354052605</v>
       </c>
       <c r="J7" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K7" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08103744079813902</v>
+        <v>0.08007299828032965</v>
       </c>
       <c r="M7" t="n">
-        <v>2.909201204226575</v>
+        <v>2.909068210601955</v>
       </c>
       <c r="N7" t="n">
-        <v>14.76382523046403</v>
+        <v>14.74488842637927</v>
       </c>
       <c r="O7" t="n">
-        <v>3.842372344068704</v>
+        <v>3.839907346066995</v>
       </c>
       <c r="P7" t="n">
-        <v>313.3273930122457</v>
+        <v>313.3414180128571</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -22043,28 +22095,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03176828225279255</v>
+        <v>0.02870220429198197</v>
       </c>
       <c r="J8" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K8" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004942395670573307</v>
+        <v>0.004024769207435108</v>
       </c>
       <c r="M8" t="n">
-        <v>2.625535658786814</v>
+        <v>2.636221178768903</v>
       </c>
       <c r="N8" t="n">
-        <v>11.30691102294974</v>
+        <v>11.37680642085163</v>
       </c>
       <c r="O8" t="n">
-        <v>3.362575058336949</v>
+        <v>3.372952181821088</v>
       </c>
       <c r="P8" t="n">
-        <v>323.4194407296109</v>
+        <v>323.4523628209851</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -22121,28 +22173,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.01708841701313423</v>
+        <v>-0.02003100179442369</v>
       </c>
       <c r="J9" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K9" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002098522797829738</v>
+        <v>0.002863144500882542</v>
       </c>
       <c r="M9" t="n">
-        <v>2.194114474222119</v>
+        <v>2.201275414303397</v>
       </c>
       <c r="N9" t="n">
-        <v>7.727222863505742</v>
+        <v>7.798285859205328</v>
       </c>
       <c r="O9" t="n">
-        <v>2.779788276740828</v>
+        <v>2.792541111461983</v>
       </c>
       <c r="P9" t="n">
-        <v>326.3066096923508</v>
+        <v>326.3382057725172</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -22199,28 +22251,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1129971204868018</v>
+        <v>0.1107194601887071</v>
       </c>
       <c r="J10" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K10" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09571414739156303</v>
+        <v>0.09202031771781982</v>
       </c>
       <c r="M10" t="n">
-        <v>2.096232884288291</v>
+        <v>2.102569873482731</v>
       </c>
       <c r="N10" t="n">
-        <v>6.712899589718448</v>
+        <v>6.750293111488615</v>
       </c>
       <c r="O10" t="n">
-        <v>2.590926396044173</v>
+        <v>2.598132620073236</v>
       </c>
       <c r="P10" t="n">
-        <v>324.0503917110419</v>
+        <v>324.0748481473791</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -22277,28 +22329,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08001260497048374</v>
+        <v>-0.08262369826738002</v>
       </c>
       <c r="J11" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K11" t="n">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06149365958532449</v>
+        <v>0.06483877409325178</v>
       </c>
       <c r="M11" t="n">
-        <v>1.863084772871162</v>
+        <v>1.871442598356015</v>
       </c>
       <c r="N11" t="n">
-        <v>5.437127138350439</v>
+        <v>5.494690902981764</v>
       </c>
       <c r="O11" t="n">
-        <v>2.331764811971919</v>
+        <v>2.344075703338475</v>
       </c>
       <c r="P11" t="n">
-        <v>329.9794498017637</v>
+        <v>330.0074864835461</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -22336,7 +22388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L402"/>
+  <dimension ref="A1:L403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47263,6 +47315,68 @@
         </is>
       </c>
     </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-42.74882800189772,173.39373082547002</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-42.749435748031125,173.39338015761467</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-42.75006708745532,173.39305866996997</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-42.75070972812951,173.3927821770468</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-42.75132564345804,173.39254979457624</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>-42.75187006475329,173.3921463214296</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>-42.75246157513079,173.3917470965568</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>-42.753101642919916,173.39144100981179</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>-42.75372260297489,173.39115613262427</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>-42.754325107151786,173.39080679758624</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
